--- a/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
+++ b/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\Absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717C2513-43C6-480C-BA25-87F957AA2B34}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4899B4D4-3A57-40BC-80A2-E123CE60D156}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="37635" windowHeight="21840" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
   <si>
     <t>NAMA</t>
   </si>
@@ -218,13 +218,22 @@
 Terima kasih…</t>
   </si>
   <si>
-    <t>13 Februari 2026</t>
-  </si>
-  <si>
-    <t>24 Februari 2026</t>
-  </si>
-  <si>
     <t>: APRIL 2026</t>
+  </si>
+  <si>
+    <t>10 April 2026</t>
+  </si>
+  <si>
+    <t>17 April 2026</t>
+  </si>
+  <si>
+    <t>Pemulihan</t>
+  </si>
+  <si>
+    <t>Antar anak ke dokter</t>
+  </si>
+  <si>
+    <t>Masih di jalan</t>
   </si>
 </sst>
 </file>
@@ -615,17 +624,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -796,96 +795,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -917,22 +826,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}" name="Table1" displayName="Table1" ref="M10:N21" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}" name="Table1" displayName="Table1" ref="M10:N21" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="M10:N21" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7BD02032-E365-49A8-ADAB-44D6FB3AFCD1}" name="Nama" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{41948D79-27FC-4502-92CC-571E48B0487D}" name="Nomor WA" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{7BD02032-E365-49A8-ADAB-44D6FB3AFCD1}" name="Nama" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{41948D79-27FC-4502-92CC-571E48B0487D}" name="Nomor WA" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}" name="Table2" displayName="Table2" ref="P26:Q27" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}" name="Table2" displayName="Table2" ref="P26:Q27" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="P26:Q27" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{84005749-F834-45CA-94CD-2EDD5B1E1F63}" name="Teks WA 1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{29720DB4-DB3A-41BE-9B35-9301A3705ADA}" name="Teks WA 2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{84005749-F834-45CA-94CD-2EDD5B1E1F63}" name="Teks WA 1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{29720DB4-DB3A-41BE-9B35-9301A3705ADA}" name="Teks WA 2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1320,7 +1229,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1387,19 +1296,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="18" t="b">
         <f>C10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="18" t="b">
         <f>F10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="11"/>
       <c r="J10" s="41" t="s">
@@ -1422,19 +1331,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="18" t="b">
         <f t="shared" ref="D11:D21" si="0">C11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="18" t="b">
         <f t="shared" ref="G11:G21" si="1">F11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="10"/>
       <c r="J11" s="23" t="s">
@@ -1452,7 +1361,7 @@
       </c>
       <c r="P11" s="1" t="str">
         <f>IF(AND(C11=FALSE,E11="",F11=FALSE,H11=""),"https://wa.me/"&amp;N11&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q$27,"[nama]",M11),"[tanggal_1]",TEXT($C$25,"dd mmmm yyyy")),"[tanggal_2]",TEXT($F$25,"dd mmmm yyyy"))),IF(AND(C11=FALSE,E11=""),"https://wa.me/"&amp;N11&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE($P$27,"[nama]",M11),"[tanggal]",TEXT($C$25,"dd mmmm yyyy"))),IF(AND(F11=FALSE,H11=""),"https://wa.me/"&amp;N11&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE($P$27,"[nama]",M11),"[tanggal]",TEXT($F$25,"dd mmmm yyyy"))),"")))</f>
-        <v>https://wa.me/6282123226368?text=Assalamualaikum%20Latip%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1463,19 +1372,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="11"/>
       <c r="J12" s="23" t="s">
@@ -1493,7 +1402,7 @@
       </c>
       <c r="P12" s="1" t="str">
         <f t="shared" ref="P12:P21" si="2">IF(AND(C12=FALSE,E12="",F12=FALSE,H12=""),"https://wa.me/"&amp;N12&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q$27,"[nama]",M12),"[tanggal_1]",TEXT($C$25,"dd mmmm yyyy")),"[tanggal_2]",TEXT($F$25,"dd mmmm yyyy"))),IF(AND(C12=FALSE,E12=""),"https://wa.me/"&amp;N12&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE($P$27,"[nama]",M12),"[tanggal]",TEXT($C$25,"dd mmmm yyyy"))),IF(AND(F12=FALSE,H12=""),"https://wa.me/"&amp;N12&amp;"?text="&amp;_xlfn.ENCODEURL(SUBSTITUTE(SUBSTITUTE($P$27,"[nama]",M12),"[tanggal]",TEXT($F$25,"dd mmmm yyyy"))),"")))</f>
-        <v>https://wa.me/6282350645281?text=Assalamualaikum%20Pak%20Udin%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1504,19 +1413,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="11"/>
       <c r="L13" s="3"/>
@@ -1528,7 +1437,7 @@
       </c>
       <c r="P13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282320040021?text=Assalamualaikum%20Mas%20Aswan%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1539,19 +1448,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="10"/>
       <c r="M14" s="1" t="s">
@@ -1562,7 +1471,7 @@
       </c>
       <c r="P14" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6281350170682?text=Assalamualaikum%20Pak%20Danik%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1579,13 +1488,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="F15" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="10"/>
       <c r="M15" s="1" t="s">
@@ -1596,7 +1507,7 @@
       </c>
       <c r="P15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6281347471525?text=Assalamualaikum%20Pak%20Mamat%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1607,11 +1518,11 @@
         <v>13</v>
       </c>
       <c r="C16" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="18" t="b">
@@ -1630,7 +1541,7 @@
       </c>
       <c r="P16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6285255990709?text=Assalamualaikum%20Mas%20Firman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v>https://wa.me/6285255990709?text=Assalamualaikum%20Mas%20Firman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1641,11 +1552,11 @@
         <v>14</v>
       </c>
       <c r="C17" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="18" t="b">
@@ -1664,7 +1575,7 @@
       </c>
       <c r="P17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282124386879?text=Assalamualaikum%20Mas%20Suhud%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v>https://wa.me/6282124386879?text=Assalamualaikum%20Mas%20Suhud%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1698,7 +1609,7 @@
       </c>
       <c r="P18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282354144365?text=Assalamualaikum%20Mas%20Salman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v>https://wa.me/6282354144365?text=Assalamualaikum%20Mas%20Salman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2010%20April%202026%20dan%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1709,19 +1620,19 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="11"/>
       <c r="M19" s="1" t="s">
@@ -1732,7 +1643,7 @@
       </c>
       <c r="P19" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6285250888733?text=Assalamualaikum%20Mas%20Reza%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1749,7 +1660,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="F20" s="18" t="b">
         <v>0</v>
       </c>
@@ -1757,7 +1670,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="11" t="s">
+        <v>64</v>
+      </c>
       <c r="M20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1766,7 +1681,7 @@
       </c>
       <c r="P20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6281220142015?text=Assalamualaikum%20Pak%20Syakur%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1800,7 +1715,7 @@
       </c>
       <c r="P21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282229432434?text=Assalamualaikum%20Mas%20Wahap%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2013%20Februari%202026%20dan%20tanggal%2024%20Februari%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v>https://wa.me/6282229432434?text=Assalamualaikum%20Mas%20Wahap%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2010%20April%202026%20dan%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1810,20 +1725,20 @@
       </c>
       <c r="C22" s="20">
         <f>SUM(COUNTIF(C10:C21,TRUE))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D22" s="20">
         <f>SUM(COUNTIF(D10:D21,TRUE))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="20">
         <f t="shared" ref="F22:G22" si="3">SUM(COUNTIF(F10:F21,TRUE))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G22" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="19"/>
     </row>
@@ -1834,29 +1749,29 @@
       </c>
       <c r="C23" s="33">
         <f>C22/$A$21*100</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="D23" s="33">
         <f>D22/$A$21*100</f>
-        <v>0</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="33">
         <f>F22/$A$21*100</f>
-        <v>0</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="G23" s="33">
         <f>G22/$A$21*100</f>
-        <v>0</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="H23" s="19"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C25" s="37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1891,17 +1806,17 @@
     <mergeCell ref="F5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="C10:D21">
-    <cfRule type="cellIs" dxfId="20" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="32" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G21">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F21">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2248,7 +2163,7 @@
     <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="C10:D21">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
+++ b/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\Absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4899B4D4-3A57-40BC-80A2-E123CE60D156}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48048DBD-C8AD-4C81-9FCB-8EE2A8AE7EAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="37635" windowHeight="21840" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>NAMA</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Masih di jalan</t>
+  </si>
+  <si>
+    <t>Ke rumah bapak di Loa Duri</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1158,7 @@
     <col min="3" max="4" width="7.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" style="13" customWidth="1"/>
     <col min="6" max="7" width="7.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.85546875" style="1"/>
     <col min="10" max="10" width="6" style="1" customWidth="1"/>
     <col min="11" max="12" width="9.85546875" style="1" customWidth="1"/>
@@ -1532,7 +1535,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="M16" s="1" t="s">
         <v>48</v>
       </c>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="P16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6285255990709?text=Assalamualaikum%20Mas%20Firman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">

--- a/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
+++ b/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\Absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48048DBD-C8AD-4C81-9FCB-8EE2A8AE7EAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D96469C-685E-4F82-8437-96390F1D954D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="37635" windowHeight="21840" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
   <si>
     <t>NAMA</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>Ke rumah bapak di Loa Duri</t>
+  </si>
+  <si>
+    <t>Dinas</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1600,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="F18" s="18" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1610,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="M18" s="1" t="s">
         <v>50</v>
       </c>
@@ -1614,7 +1621,7 @@
       </c>
       <c r="P18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282354144365?text=Assalamualaikum%20Mas%20Salman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2010%20April%202026%20dan%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">

--- a/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
+++ b/Absen/5. April 2026 - TARBIYAH & DAKWAH DT-R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\Absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D96469C-685E-4F82-8437-96390F1D954D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA833FA5-284E-4FC7-A665-14BFCAF0DB17}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="37635" windowHeight="21840" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>NAMA</t>
   </si>
@@ -240,6 +240,15 @@
   </si>
   <si>
     <t>Dinas</t>
+  </si>
+  <si>
+    <t>Ketiduran</t>
+  </si>
+  <si>
+    <t>Masih di kampung</t>
+  </si>
+  <si>
+    <t>Kerja</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1583,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="M17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1583,7 +1594,7 @@
       </c>
       <c r="P17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282124386879?text=Assalamualaikum%20Mas%20Suhud%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1710,7 +1721,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="F21" s="18" t="b">
         <v>0</v>
       </c>
@@ -1718,7 +1731,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="M21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1727,7 +1742,7 @@
       </c>
       <c r="P21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282229432434?text=Assalamualaikum%20Mas%20Wahap%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2010%20April%202026%20dan%20tanggal%2017%20April%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
